--- a/owlcms/src/main/resources/templates/protocol/Protocol-A4.xlsx
+++ b/owlcms/src/main/resources/templates/protocol/Protocol-A4.xlsx
@@ -1842,358 +1842,358 @@
       <left/>
       <right/>
       <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left/>
@@ -2201,8 +2201,8 @@
       <top style="thin">
         <color indexed="8"/>
       </top>
-      <diagonal/>
-      <bottom/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left/>
@@ -2210,8 +2210,8 @@
       <top style="thin">
         <color indexed="8"/>
       </top>
-      <diagonal/>
-      <bottom/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left/>
@@ -2219,50 +2219,50 @@
       <top style="thin">
         <color indexed="8"/>
       </top>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left/>
@@ -2270,8 +2270,8 @@
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <diagonal/>
-      <bottom/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left/>
@@ -2279,8 +2279,8 @@
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <diagonal/>
-      <bottom/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left/>
@@ -2288,8 +2288,8 @@
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <diagonal/>
-      <bottom/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left/>
@@ -2297,8 +2297,8 @@
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <diagonal/>
-      <bottom/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left/>
@@ -2306,8 +2306,8 @@
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <diagonal/>
-      <bottom/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left/>
@@ -2315,8 +2315,8 @@
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <diagonal/>
-      <bottom/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left/>
@@ -2324,8 +2324,8 @@
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <diagonal/>
-      <bottom/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left/>
@@ -2333,8 +2333,8 @@
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <diagonal/>
-      <bottom/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left/>
@@ -2342,134 +2342,134 @@
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="19">
@@ -2950,16 +2950,16 @@
       <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
     </xf>
     <xf numFmtId="49" fontId="71" fillId="0" borderId="64" xfId="0" applyNumberFormat="1" applyBorder="1" applyProtection="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="0"/>
       <protection locked="0"/>
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="0"/>
     </xf>
     <xf numFmtId="49" fontId="72" fillId="0" borderId="65" xfId="0" applyNumberFormat="1" applyBorder="1" applyProtection="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
       <protection locked="0"/>
-      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
     </xf>
     <xf numFmtId="49" fontId="73" fillId="0" borderId="66" xfId="0" applyNumberFormat="1" applyBorder="1" applyProtection="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
       <protection locked="0"/>
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
     </xf>
     <xf numFmtId="0" fontId="74" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="0"/>
@@ -3109,16 +3109,16 @@
       <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
     </xf>
     <xf numFmtId="0" fontId="122" fillId="0" borderId="115" xfId="0" applyFont="1" applyProtection="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="0"/>
       <protection locked="0"/>
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="0"/>
     </xf>
     <xf numFmtId="0" fontId="123" fillId="0" borderId="116" xfId="0" applyFont="1" applyProtection="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
       <protection locked="0"/>
-      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
     </xf>
     <xf numFmtId="0" fontId="124" fillId="0" borderId="117" xfId="0" applyFont="1" applyProtection="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
       <protection locked="0"/>
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
     </xf>
     <xf numFmtId="1" fontId="125" fillId="0" borderId="118" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="0"/>
@@ -3158,8 +3158,8 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="49" fontId="73" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="0" applyProtection="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
       <protection locked="0"/>
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
     </xf>
     <xf numFmtId="0" fontId="91" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyBorder="0">
       <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
@@ -3172,8 +3172,8 @@
       <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
     </xf>
     <xf numFmtId="0" fontId="124" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1" applyAlignment="1" applyBorder="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
       <protection locked="0"/>
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
     </xf>
     <xf numFmtId="0" fontId="134" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyBorder="0" applyFont="1">
       <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
@@ -4656,21 +4656,6 @@
     <mergeCell ref="A4:C4"/>
     <mergeCell ref="D4:V4"/>
   </mergeCells>
-  <conditionalFormatting sqref="C8:D8">
-    <cfRule type="expression" dxfId="2" priority="7" stopIfTrue="1">
-      <formula>AND((#REF!),#REF!,#REF!)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D10:E10">
-    <cfRule type="expression" dxfId="1" priority="11" stopIfTrue="1">
-      <formula>AND((#REF!),#REF!,#REF!)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D11:F13">
-    <cfRule type="expression" dxfId="0" priority="5" stopIfTrue="1">
-      <formula>AND((#REF!),#REF!,#REF!)</formula>
-    </cfRule>
-  </conditionalFormatting>
   <dataValidations count="4">
     <dataValidation showErrorMessage="1" sqref="K4 F23 C20 C17 S17 L17 F17 F20 C23 L20 S20 S23" ns1:uid="{00000000-0002-0000-0000-000000000000}"/>
     <dataValidation allowBlank="1" showErrorMessage="1" sqref="H10" ns1:uid="{00000000-0002-0000-0000-000001000000}"/>
@@ -4683,7 +4668,6 @@
       <formula2>200</formula2>
     </dataValidation>
   </dataValidations>
-  <hyperlinks/>
   <pageMargins left="0.31496062992125984" right="0.35433070866141736" top="0.39370078740157483" bottom="0.39370078740157483" header="0.51181102362204722" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="70" firstPageNumber="0" fitToHeight="0" orientation="landscape" horizontalDpi="300" verticalDpi="300" ns3:id="rId3"/>
   <headerFooter alignWithMargins="0"/>
